--- a/data/trans_camb/P45C_R1-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P45C_R1-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,17</t>
+          <t>-0,77; 1,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 0,87</t>
+          <t>-0,93; 1,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,01; 3,03</t>
+          <t>0,12; 3,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 1,31</t>
+          <t>-0,31; 1,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,56</t>
+          <t>-0,94; 0,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,94</t>
+          <t>-0,61; 1,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,95</t>
+          <t>-0,3; 1,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,5</t>
+          <t>-0,77; 0,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 1,41</t>
+          <t>-0,15; 1,39</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-60,79; 194,17</t>
+          <t>-55,18; 171,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-71,7; 155,55</t>
+          <t>-70,01; 167,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,93; 453,88</t>
+          <t>-3,27; 543,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-37,35; 182,15</t>
+          <t>-24,14; 222,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-74,58; 93,88</t>
+          <t>-67,62; 91,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-52,4; 140,51</t>
+          <t>-47,81; 168,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,91; 122,34</t>
+          <t>-24,79; 138,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-55,44; 71,76</t>
+          <t>-59,39; 68,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-18,36; 183,69</t>
+          <t>-14,44; 177,02</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,15</t>
+          <t>-1,7; 0,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,07; -0,4</t>
+          <t>-2,15; -0,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 0,27</t>
+          <t>-1,81; 0,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,37</t>
+          <t>-1,47; 0,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 0,0</t>
+          <t>-1,69; 0,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,17</t>
+          <t>-1,55; 0,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,06</t>
+          <t>-1,24; -0,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; -0,38</t>
+          <t>-1,65; -0,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; -0,09</t>
+          <t>-1,38; -0,05</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-60,86; 11,43</t>
+          <t>-62,27; 14,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-75,36; -21,02</t>
+          <t>-76,87; -21,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-66,31; 18,43</t>
+          <t>-65,28; 16,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-57,95; 25,11</t>
+          <t>-56,37; 29,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-67,18; 3,37</t>
+          <t>-65,67; 5,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-61,11; 11,1</t>
+          <t>-60,28; 16,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,74; 4,7</t>
+          <t>-51,8; -0,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-65,12; -21,25</t>
+          <t>-65,5; -20,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-55,33; -3,57</t>
+          <t>-56,22; -2,29</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,9</t>
+          <t>-2,36; 0,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 0,69</t>
+          <t>-2,63; 0,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 1,86</t>
+          <t>-1,56; 2,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 2,41</t>
+          <t>-1,79; 2,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 0,29</t>
+          <t>-2,88; 0,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 1,2</t>
+          <t>-2,11; 1,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,21</t>
+          <t>-1,39; 1,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 0,14</t>
+          <t>-2,07; 0,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 1,17</t>
+          <t>-1,34; 1,09</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-85,18; 133,6</t>
+          <t>-89,2; 114,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 148,95</t>
+          <t>-100,0; 120,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-67,87; 233,12</t>
+          <t>-62,57; 254,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-58,28; 178,84</t>
+          <t>-59,77; 167,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-87,8; 39,19</t>
+          <t>-86,46; 36,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,78; 92,63</t>
+          <t>-63,8; 118,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-57,49; 84,05</t>
+          <t>-53,23; 89,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-80,51; 21,35</t>
+          <t>-77,59; 20,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-48,86; 91,89</t>
+          <t>-49,5; 91,04</t>
         </is>
       </c>
     </row>
@@ -1325,37 +1325,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,16</t>
+          <t>-1,04; 0,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; -0,2</t>
+          <t>-1,37; -0,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,63</t>
+          <t>-0,84; 0,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,59</t>
+          <t>-0,67; 0,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,06</t>
+          <t>-1,16; -0,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,31</t>
+          <t>-0,84; 0,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,21</t>
+          <t>-0,66; 0,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,28</t>
+          <t>-0,64; 0,3</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-49,78; 12,42</t>
+          <t>-52,25; 13,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-66,86; -11,59</t>
+          <t>-66,44; -13,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-40,59; 49,05</t>
+          <t>-40,23; 48,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-34,17; 45,06</t>
+          <t>-34,15; 40,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-57,04; 4,81</t>
+          <t>-57,2; 0,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-43,47; 22,94</t>
+          <t>-42,7; 25,69</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-36,01; 14,39</t>
+          <t>-34,27; 13,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-56,25; -18,84</t>
+          <t>-56,78; -18,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-32,19; 19,69</t>
+          <t>-33,48; 19,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P45C_R1-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P45C_R1-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,31</t>
+          <t>1,16</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,03</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>0,49</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 1,04</t>
+          <t>-0,71; 1,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,02</t>
+          <t>-0,94; 0,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 3,04</t>
+          <t>-0,12; 2,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,37</t>
+          <t>-0,36; 1,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,61</t>
+          <t>-0,98; 0,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,03</t>
+          <t>-0,68; 0,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,05</t>
+          <t>-0,33; 0,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,47</t>
+          <t>-0,7; 0,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 1,39</t>
+          <t>-0,18; 1,25</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>132,76%</t>
+          <t>117,16%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>48,44%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-55,18; 171,24</t>
+          <t>-52,3; 195,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-70,01; 167,1</t>
+          <t>-68,3; 161,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 543,54</t>
+          <t>-22,83; 384,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,14; 222,69</t>
+          <t>-29,18; 193,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-67,62; 91,31</t>
+          <t>-73,65; 99,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,81; 168,0</t>
+          <t>-49,89; 137,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-24,79; 138,25</t>
+          <t>-25,8; 133,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,39; 68,0</t>
+          <t>-55,11; 75,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 177,02</t>
+          <t>-15,27; 167,21</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,7</t>
+          <t>-0,55</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,67</t>
+          <t>-0,5</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,69</t>
+          <t>-0,53</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,17</t>
+          <t>-1,56; 0,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; -0,4</t>
+          <t>-2,08; -0,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 0,24</t>
+          <t>-1,57; 0,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,4</t>
+          <t>-1,53; 0,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,05</t>
+          <t>-1,71; 0,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 0,21</t>
+          <t>-1,41; 0,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; -0,0</t>
+          <t>-1,25; 0,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; -0,36</t>
+          <t>-1,68; -0,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,38; -0,05</t>
+          <t>-1,16; 0,21</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-33,36%</t>
+          <t>-26,26%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-33,15%</t>
+          <t>-24,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-33,28%</t>
+          <t>-25,45%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-62,27; 14,04</t>
+          <t>-57,68; 17,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-76,87; -21,29</t>
+          <t>-76,54; -20,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-65,28; 16,3</t>
+          <t>-58,17; 31,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-56,37; 29,5</t>
+          <t>-58,79; 22,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-65,67; 5,11</t>
+          <t>-66,48; 9,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-60,28; 16,44</t>
+          <t>-53,72; 24,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,8; -0,06</t>
+          <t>-51,12; 0,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-65,5; -20,66</t>
+          <t>-65,72; -21,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-56,22; -2,29</t>
+          <t>-47,43; 12,79</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,28</t>
+          <t>-0,1</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>0,04</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 0,88</t>
+          <t>-2,21; 0,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 0,59</t>
+          <t>-2,61; 0,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,05</t>
+          <t>-1,58; 1,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 2,24</t>
+          <t>-1,65; 2,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 0,34</t>
+          <t>-2,89; 0,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 1,39</t>
+          <t>-1,88; 1,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 1,09</t>
+          <t>-1,38; 1,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 0,15</t>
+          <t>-2,2; 0,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,09</t>
+          <t>-1,33; 1,2</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-12,83%</t>
+          <t>-4,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-5,07%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-89,2; 114,32</t>
+          <t>-84,49; 128,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 120,01</t>
+          <t>-100,0; 120,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-62,57; 254,42</t>
+          <t>-67,39; 189,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-59,77; 167,5</t>
+          <t>-56,84; 228,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-86,46; 36,27</t>
+          <t>-86,44; 38,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-63,8; 118,82</t>
+          <t>-57,2; 127,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-53,23; 89,17</t>
+          <t>-54,79; 85,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-77,59; 20,38</t>
+          <t>-80,61; 16,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-49,5; 91,04</t>
+          <t>-47,83; 92,97</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>0,03</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,26</t>
+          <t>-0,13</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>-0,05</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,17</t>
+          <t>-1,1; 0,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; -0,18</t>
+          <t>-1,38; -0,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 0,63</t>
+          <t>-0,63; 0,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,56</t>
+          <t>-0,67; 0,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,16; -0,01</t>
+          <t>-1,14; -0,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 0,33</t>
+          <t>-0,69; 0,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,2</t>
+          <t>-0,67; 0,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,12; -0,28</t>
+          <t>-1,1; -0,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,3</t>
+          <t>-0,48; 0,36</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-4,85%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-15,3%</t>
+          <t>-7,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-10,21%</t>
+          <t>-3,2%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-52,25; 13,2</t>
+          <t>-51,01; 18,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-66,44; -13,18</t>
+          <t>-67,23; -10,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-40,23; 48,73</t>
+          <t>-32,28; 62,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-34,15; 40,74</t>
+          <t>-34,18; 42,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-57,2; 0,44</t>
+          <t>-56,94; 0,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-42,7; 25,69</t>
+          <t>-34,44; 38,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-34,27; 13,73</t>
+          <t>-35,41; 12,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-56,78; -18,69</t>
+          <t>-56,4; -15,89</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-33,48; 19,69</t>
+          <t>-25,33; 23,9</t>
         </is>
       </c>
     </row>
